--- a/March_Release_SCB_UAT/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>696724</v>
+        <v>573294</v>
       </c>
       <c r="D2" t="str">
-        <v>Leland</v>
+        <v>Kristin</v>
       </c>
       <c r="E2" t="str">
         <v>4408</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>6641634148</v>
+        <v>1373244989</v>
       </c>
       <c r="O2" t="str">
-        <v>leland@yopmail.com</v>
+        <v>kristin@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>

--- a/March_Release_SCB_UAT/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>573294</v>
+        <v>520068</v>
       </c>
       <c r="D2" t="str">
-        <v>Kristin</v>
+        <v>Melvin</v>
       </c>
       <c r="E2" t="str">
         <v>4408</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>1373244989</v>
+        <v>3330774201</v>
       </c>
       <c r="O2" t="str">
-        <v>kristin@yopmail.com</v>
+        <v>melvin@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>

--- a/March_Release_SCB_UAT/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,13 +466,13 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>520068</v>
+        <v>693827</v>
       </c>
       <c r="D2" t="str">
-        <v>Melvin</v>
+        <v>Shana</v>
       </c>
       <c r="E2" t="str">
-        <v>4408</v>
+        <v>2256</v>
       </c>
       <c r="F2" t="str">
         <v>Collections</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>3330774201</v>
+        <v>7300260237</v>
       </c>
       <c r="O2" t="str">
-        <v>melvin@yopmail.com</v>
+        <v>shana@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
@@ -514,7 +514,7 @@
         <v>10-10-2032</v>
       </c>
       <c r="S2" t="str">
-        <v>Bulk upl$%56oad</v>
+        <v>Bulk up56oad</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_SCB_UAT/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>693827</v>
+        <v>698802</v>
       </c>
       <c r="D2" t="str">
-        <v>Shana</v>
+        <v>Jazlyn</v>
       </c>
       <c r="E2" t="str">
         <v>2256</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>7300260237</v>
+        <v>7332835197</v>
       </c>
       <c r="O2" t="str">
-        <v>shana@yopmail.com</v>
+        <v>jazlyn@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
